--- a/reports/Nandha_Engineering_College_Weekly_Contest_516_CSE_Cyber_Security_III_Year.xlsx
+++ b/reports/Nandha_Engineering_College_Weekly_Contest_516_CSE_Cyber_Security_III_Year.xlsx
@@ -1124,7 +1124,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>13</v>
@@ -1264,7 +1264,7 @@
         <v>11</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1342,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -1554,10 +1554,10 @@
         <v>11</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -1864,10 +1864,10 @@
         <v>11</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1935,7 +1935,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>SHREE SANJAY U K</t>
+          <t>AMRUTHA M</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>732224CCL03</t>
+          <t>732224CC002</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -2229,15 +2229,15 @@
         <v>1</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="19" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>AMRUTHA M</t>
+          <t>BHARATH G</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>732224CC002</t>
+          <t>732224CC004</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>BHARATH G</t>
+          <t>DHARUNRAJ K P</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>732224CC004</t>
+          <t>732224CC008</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>DHARUNRAJ K P</t>
+          <t>GOKUL P</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>732224CC008</t>
+          <t>732224CC010</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>GOKUL P</t>
+          <t>HARISH KUMAAR S</t>
         </is>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>732224CC010</t>
+          <t>732224CC014</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>HARISH KUMAAR S</t>
+          <t>JANANI S</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>732224CC014</t>
+          <t>732224CC017</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>JANANI S</t>
+          <t>RAJESH R</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>732224CC017</t>
+          <t>732224CC039</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>RAJESH R</t>
+          <t>SARAN.R</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>732224CC039</t>
+          <t>732224CCL02</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>SARAN.R</t>
+          <t>SHREE SANJAY U K</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>732224CCL02</t>
+          <t>732224CCL03</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="G9" s="19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -3336,7 +3336,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>94a47e67d366d22e1757b2ae77b691f59675b55b30e47fcbdda70706d832bde9</t>
+          <t>94c6d6eeefb395d95ef4c0a70598359d4f6ef0e639b9ee548c189ac04cb3fe6d</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -11372,15 +11372,15 @@
         <v>1</v>
       </c>
       <c r="J69" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" s="22" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="L69" s="22" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -11500,7 +11500,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -11573,12 +11573,12 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>732224CCL03</t>
+          <t>732224CC002</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>SHREE SANJAY U K</t>
+          <t>AMRUTHA M</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>shreesanjay</t>
+          <t>Amruthauma</t>
         </is>
       </c>
       <c r="G8" s="19" t="n">
@@ -11606,15 +11606,15 @@
         <v>1</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="L8" s="23" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>732224CC002</t>
+          <t>732224CC004</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>AMRUTHA M</t>
+          <t>BHARATH G</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Amruthauma</t>
+          <t>BHARATH1927</t>
         </is>
       </c>
       <c r="G9" s="19" t="n">
@@ -11673,12 +11673,12 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>732224CC004</t>
+          <t>732224CC008</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>BHARATH G</t>
+          <t>DHARUNRAJ K P</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>BHARATH1927</t>
+          <t>K_P_DHARUNRAJ</t>
         </is>
       </c>
       <c r="G10" s="19" t="n">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>732224CC008</t>
+          <t>732224CC010</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>DHARUNRAJ K P</t>
+          <t>GOKUL P</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>K_P_DHARUNRAJ</t>
+          <t>gokul_5405</t>
         </is>
       </c>
       <c r="G11" s="19" t="n">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>732224CC010</t>
+          <t>732224CC014</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>GOKUL P</t>
+          <t>HARISH KUMAAR S</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>gokul_5405</t>
+          <t>HarishVichu</t>
         </is>
       </c>
       <c r="G12" s="19" t="n">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>732224CC014</t>
+          <t>732224CC017</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>HARISH KUMAAR S</t>
+          <t>JANANI S</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>HarishVichu</t>
+          <t>Jananii_26</t>
         </is>
       </c>
       <c r="G13" s="19" t="n">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>732224CC017</t>
+          <t>732224CC039</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>JANANI S</t>
+          <t>RAJESH R</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Jananii_26</t>
+          <t>Rajesh1328</t>
         </is>
       </c>
       <c r="G14" s="19" t="n">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>732224CC039</t>
+          <t>732224CCL02</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>RAJESH R</t>
+          <t>SARAN.R</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>Rajesh1328</t>
+          <t>Saranraj_2580</t>
         </is>
       </c>
       <c r="G15" s="19" t="n">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>732224CCL02</t>
+          <t>732224CCL03</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>SARAN.R</t>
+          <t>SHREE SANJAY U K</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Saranraj_2580</t>
+          <t>shreesanjay</t>
         </is>
       </c>
       <c r="G16" s="19" t="n">
@@ -12886,12 +12886,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -12927,14 +12927,14 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>WEEKLY CONTEST 516 — 4/4 PERFECT SOLVERS (1 STUDENTS)</t>
+          <t>WEEKLY CONTEST 516 — 4/4 PERFECT SOLVERS (0 STUDENTS)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -12999,56 +12999,6 @@
         <is>
           <t>Score</t>
         </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>732224CCL03</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>SHREE SANJAY U K</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>CSE(CS)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>shreesanjay</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="23" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="L8" s="23" t="n">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -13070,12 +13020,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -13111,14 +13061,14 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>WEEKLY CONTEST 516 — 3/4 SOLVERS (10 STUDENTS)</t>
+          <t>WEEKLY CONTEST 516 — 3/4 SOLVERS (11 STUDENTS)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -13591,12 +13541,12 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>732224CCL04</t>
+          <t>732224CCL03</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>SRIDHAR S</t>
+          <t>SHREE SANJAY U K</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -13611,7 +13561,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>sridhar320076</t>
+          <t>shreesanjay</t>
         </is>
       </c>
       <c r="G16" s="19" t="n">
@@ -13641,47 +13591,97 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
+          <t>732224CCL04</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>SRIDHAR S</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>CSE(CS)</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>sridhar320076</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="L17" s="23" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
           <t>732224CC059</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>YURJEEN J</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>CSE(CS)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>CSE(CS)</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>Yurjeen26</t>
         </is>
       </c>
-      <c r="G17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="23" t="inlineStr">
+      <c r="G18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L17" s="23" t="n">
+      <c r="L18" s="23" t="n">
         <v>12</v>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14536,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:10 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
         </is>
       </c>
     </row>

--- a/reports/Nandha_Engineering_College_Weekly_Contest_516_CSE_Cyber_Security_III_Year.xlsx
+++ b/reports/Nandha_Engineering_College_Weekly_Contest_516_CSE_Cyber_Security_III_Year.xlsx
@@ -194,14 +194,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF1F2"/>
-        <bgColor rgb="00FFF1F2"/>
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECFDF5"/>
-        <bgColor rgb="00ECFDF5"/>
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1110,7 +1110,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>TOTAL INSTITUTIONAL ROSTER</t>
+          <t>TOTAL SCOPE ROSTER</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1299,7 +1299,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -1328,21 +1328,21 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>WEEKLY CONTEST 516 — ALL 11 DEPARTMENTS SUMMARY</t>
+          <t>WEEKLY CONTEST 516 — DEPARTMENTS BREAKDOWN</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>INSTITUTIONAL TOTAL</t>
+          <t>TOTAL IN SCOPE</t>
         </is>
       </c>
       <c r="C19" s="24" t="n">
@@ -1889,7 +1889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1921,7 +1921,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -2600,470 +2600,670 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31"/>
+    <row r="31">
+      <c r="A31" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>YURJEEN J</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>732224CC059</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>12</v>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>DHARSHINI A M</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>732224CC006</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>GIRIPATHI K</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>732224CC009</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>KARTHIKEYAN V</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>732224CC020</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>KIRUTHIKAA P T</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>732224CC021</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>2/4</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>DEPARTMENT OF CSE(IOT) — TOP PERFORMERS (0 VERIFIED SOLVERS)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>Register No</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="G33" s="15" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H33" s="15" t="inlineStr">
+      <c r="H38" s="15" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="I33" s="15" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>Solved</t>
         </is>
       </c>
-      <c r="J33" s="15" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>No verified contest solvers recorded for CSE(IOT).</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="25" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>DEPARTMENT OF ECE — TOP PERFORMERS (0 VERIFIED SOLVERS)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>Register No</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H37" s="15" t="inlineStr">
+      <c r="H42" s="15" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>Solved</t>
         </is>
       </c>
-      <c r="J37" s="15" t="inlineStr">
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>No verified contest solvers recorded for ECE.</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>DEPARTMENT OF EEE — TOP PERFORMERS (0 VERIFIED SOLVERS)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>Register No</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="G41" s="15" t="inlineStr">
+      <c r="G46" s="15" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H41" s="15" t="inlineStr">
+      <c r="H46" s="15" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>Solved</t>
         </is>
       </c>
-      <c r="J41" s="15" t="inlineStr">
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>No verified contest solvers recorded for EEE.</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="25" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>DEPARTMENT OF MECH — TOP PERFORMERS (0 VERIFIED SOLVERS)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>Register No</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="G45" s="15" t="inlineStr">
+      <c r="G50" s="15" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H45" s="15" t="inlineStr">
+      <c r="H50" s="15" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>Solved</t>
         </is>
       </c>
-      <c r="J45" s="15" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>No verified contest solvers recorded for MECH.</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="25" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>DEPARTMENT OF CIVIL — TOP PERFORMERS (0 VERIFIED SOLVERS)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>Register No</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="F49" s="15" t="inlineStr">
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
+      <c r="G54" s="15" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H49" s="15" t="inlineStr">
+      <c r="H54" s="15" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>Solved</t>
         </is>
       </c>
-      <c r="J49" s="15" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>No verified contest solvers recorded for CIVIL.</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="25" t="inlineStr">
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>DEPARTMENT OF AGRI — TOP PERFORMERS (0 VERIFIED SOLVERS)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>Register No</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="F58" s="15" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="G53" s="15" t="inlineStr">
+      <c r="G58" s="15" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H53" s="15" t="inlineStr">
+      <c r="H58" s="15" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="I53" s="15" t="inlineStr">
+      <c r="I58" s="15" t="inlineStr">
         <is>
           <t>Solved</t>
         </is>
       </c>
-      <c r="J53" s="15" t="inlineStr">
+      <c r="J58" s="15" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>No verified contest solvers recorded for AGRI.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="25" t="inlineStr">
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>DEPARTMENT OF BME — TOP PERFORMERS (0 VERIFIED SOLVERS)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>Student Name</t>
         </is>
       </c>
-      <c r="C57" s="15" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
         <is>
           <t>Register No</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E57" s="15" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="F57" s="15" t="inlineStr">
+      <c r="F62" s="15" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="G57" s="15" t="inlineStr">
+      <c r="G62" s="15" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H57" s="15" t="inlineStr">
+      <c r="H62" s="15" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="I57" s="15" t="inlineStr">
+      <c r="I62" s="15" t="inlineStr">
         <is>
           <t>Solved</t>
         </is>
       </c>
-      <c r="J57" s="15" t="inlineStr">
+      <c r="J62" s="15" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="26" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="26" t="inlineStr">
         <is>
           <t>No verified contest solvers recorded for BME.</t>
         </is>
@@ -3071,32 +3271,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A47:J47"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A32:J32"/>
     <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A53:J53"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A63:J63"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A49:J49"/>
     <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A51:J51"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A61:J61"/>
     <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A37:J37"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A57:J57"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A42:J42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3138,7 +3338,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3352,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3322,7 +3522,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3536,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3611,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Total Institutional Students Evaluated</t>
+          <t>Scope Students Evaluated</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
@@ -3464,48 +3664,36 @@
       </c>
       <c r="C17" s="29" t="inlineStr">
         <is>
-          <t>PASS (Solved == Q1 + Q2 + Q3 + Q4 for all 1,450 records)</t>
+          <t>PASS (Solved == Q1 + Q2 + Q3 + Q4 for all records)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Department Roster Reconciliation</t>
+          <t>Reconciliation Decision</t>
         </is>
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>PASS (Sum of all 11 departments strictly equals 1,450)</t>
+          <t>FINALIZED &amp; IMMUTABLE</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>Reconciliation Decision</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="inlineStr">
-        <is>
-          <t>FINALIZED &amp; IMMUTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
           <t>Dataset SHA-256 Checksum</t>
         </is>
       </c>
-      <c r="C20" s="30" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>94c6d6eeefb395d95ef4c0a70598359d4f6ef0e639b9ee548c189ac04cb3fe6d</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="30">
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C8:F8"/>
@@ -3522,14 +3710,12 @@
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C20:F20"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
@@ -3550,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3559,6 +3745,12 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3578,21 +3770,21 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>COMPLETE INSTITUTIONAL STUDENT MASTER ROSTER (1,450 STUDENTS)</t>
+          <t>STUDENT ROSTER — ALPHABETICAL ORDER (63 STUDENTS)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -3628,6 +3820,36 @@
           <t>LeetCode Username</t>
         </is>
       </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>Solved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="n">
@@ -3635,12 +3857,12 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>732224CC044</t>
+          <t>732224CC001</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>AJAY A</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -3653,9 +3875,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>sakthi0407</t>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>Ajay_a1277</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3909,12 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>732224CC025</t>
+          <t>732224CC002</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>MAGUDAPATHI S</t>
+          <t>AMRUTHA M</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -3683,9 +3927,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>Magudapathi26</t>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Amruthauma</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3961,12 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>732224CC021</t>
+          <t>732224CC003</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>KIRUTHIKAA P T</t>
+          <t>ANUSHKUMAR R</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -3713,9 +3979,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>KIRUTHIKAA_05</t>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>anushkumar_06</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -3725,12 +4013,12 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>732224CC047</t>
+          <t>732224CC004</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>SHARMILA P</t>
+          <t>BHARATH G</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -3743,9 +4031,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>Sharmila__27</t>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>BHARATH1927</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -3755,12 +4065,12 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>732224CC035</t>
+          <t>732224CC005</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>POOMITHA KS</t>
+          <t>DHANUSHYA G K</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -3773,9 +4083,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>Poomitha_23</t>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>dhanu2006</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -3785,12 +4117,12 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>732224CC017</t>
+          <t>732224CC006</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>JANANI S</t>
+          <t>DHARSHINI A M</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -3803,9 +4135,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>Jananii_26</t>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>DHARSHINI_1605</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -3815,12 +4169,12 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>732224CC048</t>
+          <t>732224CC007</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>SOWMIYA S</t>
+          <t>DHARSHINI S M</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -3833,9 +4187,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>Sowmiya_7383</t>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Dharshini90989</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>1/4</t>
         </is>
       </c>
     </row>
@@ -3845,12 +4221,12 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>732224CC029</t>
+          <t>732224CC008</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>MOHAMED THARIQ J</t>
+          <t>DHARUNRAJ K P</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -3863,9 +4239,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>Thariq2625</t>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>K_P_DHARUNRAJ</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -3875,12 +4273,12 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>732224CC002</t>
+          <t>732224CC009</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>AMRUTHA M</t>
+          <t>GIRIPATHI K</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -3893,9 +4291,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>Amruthauma</t>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>Giripathi_k</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -3905,12 +4325,12 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>732224CC027</t>
+          <t>732224CC010</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>MANJUNATH D</t>
+          <t>GOKUL P</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -3923,9 +4343,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>ByNXF6IdWN</t>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>gokul_5405</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -3935,12 +4377,12 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>732224CC001</t>
+          <t>732224CC011</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>AJAY A</t>
+          <t>HARDIKA M</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -3953,9 +4395,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>Ajay_a1277</t>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>hardi22011</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -3965,12 +4429,12 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>732224CC003</t>
+          <t>732224CC012</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>ANUSHKUMAR R</t>
+          <t>HARIHARAN S V</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -3983,9 +4447,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>anushkumar_06</t>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>x8ggzaR6Gx</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -3995,12 +4481,12 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>732224CC004</t>
+          <t>732224CC013</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>BHARATH G</t>
+          <t>HARISH K</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -4013,9 +4499,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>BHARATH1927</t>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>Harish000007</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4533,12 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>732224CC005</t>
+          <t>732224CC014</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>DHANUSHYA G K</t>
+          <t>HARISH KUMAAR S</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -4043,9 +4551,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>dhanu2006</t>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>HarishVichu</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4585,12 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>732224CC006</t>
+          <t>732224CC015</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>DHARSHINI A M</t>
+          <t>HARISH N</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -4073,9 +4603,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>DHARSHINI_1605</t>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>Har-ish23</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4085,12 +4637,12 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>732224CC007</t>
+          <t>732224CC016</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>DHARSHINI S M</t>
+          <t>INIYA K</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -4103,9 +4655,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>Dharshini90989</t>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>Iniya3126</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4689,12 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>732224CC008</t>
+          <t>732224CC017</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>DHARUNRAJ K P</t>
+          <t>JANANI S</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -4133,9 +4707,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>K_P_DHARUNRAJ</t>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>Jananii_26</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4741,12 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>732224CC009</t>
+          <t>732224CC018</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>GIRIPATHI K</t>
+          <t>JAYAPRAKASH S</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -4163,9 +4759,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>Giripathi_k</t>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>jayaprakash2007</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4793,12 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>732224CC010</t>
+          <t>732224CC019</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>GOKUL P</t>
+          <t>JAYASURYA S</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -4193,9 +4811,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>gokul_5405</t>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>Surya1231172</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4205,12 +4845,12 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>732224CC011</t>
+          <t>732224CC020</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>HARDIKA M</t>
+          <t>KARTHIKEYAN V</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -4223,9 +4863,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>hardi22011</t>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>karthi_2007</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4897,12 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>732224CC012</t>
+          <t>732224CC021</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>HARIHARAN S V</t>
+          <t>KIRUTHIKAA P T</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
@@ -4253,9 +4915,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>x8ggzaR6Gx</t>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>KIRUTHIKAA_05</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4949,12 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>732224CC013</t>
+          <t>732224CC022</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>HARISH K</t>
+          <t>KISHORE C</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -4283,9 +4967,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>Harish000007</t>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>KISHORE_CHANDRAKUMAR</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4295,12 +5001,12 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>732224CC014</t>
+          <t>732224CC023</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>HARISH KUMAAR S</t>
+          <t>LAKSANA S</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
@@ -4313,9 +5019,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>HarishVichu</t>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>Laksana_Subramanian</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4325,12 +5053,12 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>732224CC015</t>
+          <t>732224CC024</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>HARISH N</t>
+          <t>MADAN PRASATH G</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
@@ -4343,9 +5071,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>Har-ish23</t>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4355,12 +5105,12 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>732224CC016</t>
+          <t>732224CC025</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>INIYA K</t>
+          <t>MAGUDAPATHI S</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
@@ -4373,9 +5123,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>Iniya3126</t>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>Magudapathi26</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4385,12 +5157,12 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>732224CC018</t>
+          <t>732224CC026</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>JAYAPRAKASH S</t>
+          <t>MAHILNETHRA S K</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
@@ -4403,9 +5175,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>jayaprakash2007</t>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>mahilnethra</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4415,12 +5209,12 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>732224CC019</t>
+          <t>732224CC027</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>JAYASURYA S</t>
+          <t>MANJUNATH D</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
@@ -4433,9 +5227,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>Surya1231172</t>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>ByNXF6IdWN</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4445,12 +5261,12 @@
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>732224CC020</t>
+          <t>732224CC028</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>KARTHIKEYAN V</t>
+          <t>MANOJ KUMAR C</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
@@ -4463,9 +5279,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>karthi_2007</t>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>ManojKumar2315</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4475,12 +5313,12 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>732224CC022</t>
+          <t>732224CC029</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>KISHORE C</t>
+          <t>MOHAMED THARIQ J</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
@@ -4493,9 +5331,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>KISHORE_CHANDRAKUMAR</t>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>Thariq2625</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4505,12 +5365,12 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>732224CC023</t>
+          <t>732224CCL01</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>LAKSANA S</t>
+          <t>MOHAMMED AFFAN.JA</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -4523,9 +5383,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>Laksana_Subramanian</t>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>Mohammed_Affan_JA</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4535,12 +5417,12 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>732224CC024</t>
+          <t>732224CC031</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>MADAN PRASATH G</t>
+          <t>NANTHISH S</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -4553,9 +5435,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>login</t>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>nanthishvaran_07</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4565,12 +5469,12 @@
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>732224CC026</t>
+          <t>732224CC032</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>MAHILNETHRA S K</t>
+          <t>NISHANTH J S</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
@@ -4583,9 +5487,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>mahilnethra</t>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>Nishanthjs</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4595,12 +5521,12 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>732224CC028</t>
+          <t>732224CC033</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>MANOJ KUMAR C</t>
+          <t>NITHIN S</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -4613,9 +5539,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>ManojKumar2315</t>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>nithin_31_</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4625,12 +5573,12 @@
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>732224CC031</t>
+          <t>732224CC034</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>NANTHISH S</t>
+          <t>NIVETHYTHA JR R</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -4643,9 +5591,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>nanthishvaran_07</t>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>Nivethytha0704</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4655,12 +5625,12 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>732224CC032</t>
+          <t>732224CC035</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>NISHANTH J S</t>
+          <t>POOMITHA KS</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -4673,9 +5643,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>Nishanthjs</t>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>Poomitha_23</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4685,12 +5677,12 @@
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>732224CC033</t>
+          <t>732224CC036</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>NITHIN S</t>
+          <t>PRASATH R</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -4703,9 +5695,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
-        <is>
-          <t>nithin_31_</t>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>prasath00156</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4715,12 +5729,12 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>732224CC034</t>
+          <t>732224CC037</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>NIVETHYTHA JR R</t>
+          <t>PRITHIKA P</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -4733,9 +5747,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>Nivethytha0704</t>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>Pritss2206</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4745,12 +5781,12 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>732224CC036</t>
+          <t>732224CC038</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>PRASATH R</t>
+          <t>RADHISRI N</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -4763,9 +5799,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F45" s="19" t="inlineStr">
-        <is>
-          <t>prasath00156</t>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>Radhisri28</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4775,12 +5833,12 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>732224CC037</t>
+          <t>732224CC039</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>PRITHIKA P</t>
+          <t>RAJESH R</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
@@ -4793,9 +5851,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F46" s="19" t="inlineStr">
-        <is>
-          <t>Pritss2206</t>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>Rajesh1328</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -4805,12 +5885,12 @@
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>732224CC038</t>
+          <t>732224CC040</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>RADHISRI N</t>
+          <t>RITHANIKA V</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -4823,9 +5903,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F47" s="19" t="inlineStr">
-        <is>
-          <t>Radhisri28</t>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>Rithanika_Venakatachalam</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -4835,12 +5937,12 @@
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>732224CC039</t>
+          <t>732224CC041</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>RAJESH R</t>
+          <t>RITHIKA J</t>
         </is>
       </c>
       <c r="D48" s="19" t="inlineStr">
@@ -4853,9 +5955,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F48" s="19" t="inlineStr">
-        <is>
-          <t>Rajesh1328</t>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>Rithu16122006</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4865,12 +5989,12 @@
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>732224CC040</t>
+          <t>732224CC042</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>RITHANIKA V</t>
+          <t>ROHITH R</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -4883,9 +6007,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F49" s="19" t="inlineStr">
-        <is>
-          <t>Rithanika_Venakatachalam</t>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>Rohith_2682006</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4895,12 +6041,12 @@
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>732224CC041</t>
+          <t>732224CC043</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>RITHIKA J</t>
+          <t>SABARI N</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
@@ -4913,9 +6059,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
-        <is>
-          <t>Rithu16122006</t>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>sabari43</t>
+        </is>
+      </c>
+      <c r="G50" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4925,12 +6093,12 @@
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>732224CC042</t>
+          <t>732224CC044</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>ROHITH R</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -4943,9 +6111,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
-        <is>
-          <t>Rohith_2682006</t>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>sakthi0407</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -4955,12 +6145,12 @@
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>732224CC043</t>
+          <t>732224CCL02</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>SABARI N</t>
+          <t>SARAN.R</t>
         </is>
       </c>
       <c r="D52" s="19" t="inlineStr">
@@ -4973,9 +6163,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>sabari43</t>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>Saranraj_2580</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -5003,9 +6215,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F53" s="19" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
         <is>
           <t>shandeeshrp</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5033,9 +6267,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="F54" s="20" t="inlineStr">
         <is>
           <t>Priya_1410</t>
+        </is>
+      </c>
+      <c r="G54" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5045,12 +6301,12 @@
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>732224CC049</t>
+          <t>732224CC047</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>SRISELVAN P</t>
+          <t>SHARMILA P</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -5063,9 +6319,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
-        <is>
-          <t>SriselvanP</t>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>Sharmila__27</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5075,12 +6353,12 @@
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>732224CC050</t>
+          <t>732224CCL03</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>SUBA SRI B</t>
+          <t>SHREE SANJAY U K</t>
         </is>
       </c>
       <c r="D56" s="19" t="inlineStr">
@@ -5093,9 +6371,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F56" s="19" t="inlineStr">
-        <is>
-          <t>suba_sri10</t>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>shreesanjay</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -5105,12 +6405,12 @@
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>732224CC051</t>
+          <t>732224CC048</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>SUBASH MURUGAN S</t>
+          <t>SOWMIYA S</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -5123,9 +6423,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
-        <is>
-          <t>subashmurugan212</t>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>Sowmiya_7383</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5135,12 +6457,12 @@
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>732224CC052</t>
+          <t>732224CCL04</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>SUPRIYA K</t>
+          <t>SRIDHAR S</t>
         </is>
       </c>
       <c r="D58" s="19" t="inlineStr">
@@ -5153,9 +6475,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F58" s="19" t="inlineStr">
-        <is>
-          <t>SUPRIYA_2601</t>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>sridhar320076</t>
+        </is>
+      </c>
+      <c r="G58" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -5165,12 +6509,12 @@
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>732224CC053</t>
+          <t>732224CC049</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>SURESH S</t>
+          <t>SRISELVAN P</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -5183,9 +6527,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
-        <is>
-          <t>suresh11092006</t>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>SriselvanP</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5195,12 +6561,12 @@
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>732224CC054</t>
+          <t>732224CC050</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>VARSHINI DEVI K</t>
+          <t>SUBA SRI B</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
@@ -5213,9 +6579,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
-        <is>
-          <t>varshini_devi2006</t>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>suba_sri10</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5225,12 +6613,12 @@
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>732224CC055</t>
+          <t>732224CC051</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>VEDHASREE P</t>
+          <t>SUBASH MURUGAN S</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -5243,9 +6631,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>vedhasree_2006</t>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>subashmurugan212</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5255,12 +6665,12 @@
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>732224CC056</t>
+          <t>732224CC052</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>VIGNESH T</t>
+          <t>SUPRIYA K</t>
         </is>
       </c>
       <c r="D62" s="19" t="inlineStr">
@@ -5273,9 +6683,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
-        <is>
-          <t>vignesh_1112</t>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>SUPRIYA_2601</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5285,12 +6717,12 @@
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>732224CC057</t>
+          <t>732224CC053</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>VISHAANTH M B</t>
+          <t>SURESH S</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -5303,9 +6735,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
-        <is>
-          <t>vishaanth0007</t>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>suresh11092006</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5315,12 +6769,12 @@
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>732224CC058</t>
+          <t>732224CC054</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>YAZHINI SHREE A</t>
+          <t>VARSHINI DEVI K</t>
         </is>
       </c>
       <c r="D64" s="19" t="inlineStr">
@@ -5333,9 +6787,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
-        <is>
-          <t>yazhu_shree</t>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>varshini_devi2006</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5345,12 +6821,12 @@
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>732224CC059</t>
+          <t>732224CC055</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>YURJEEN J</t>
+          <t>VEDHASREE P</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -5363,9 +6839,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F65" s="19" t="inlineStr">
-        <is>
-          <t>Yurjeen26</t>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>vedhasree_2006</t>
+        </is>
+      </c>
+      <c r="G65" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
@@ -5375,12 +6873,12 @@
       </c>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>732224CC060</t>
+          <t>732224CC056</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>YUVANESH S</t>
+          <t>VIGNESH T</t>
         </is>
       </c>
       <c r="D66" s="19" t="inlineStr">
@@ -5393,9 +6891,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
-        <is>
-          <t>V0mg69rzpB</t>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>vignesh_1112</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5405,12 +6925,12 @@
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>732224CCL01</t>
+          <t>732224CC057</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>MOHAMMED AFFAN.JA</t>
+          <t>VISHAANTH M B</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -5423,9 +6943,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>Mohammed_Affan_JA</t>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>vishaanth0007</t>
+        </is>
+      </c>
+      <c r="G67" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H67" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="21" t="inlineStr">
+        <is>
+          <t>1/4</t>
         </is>
       </c>
     </row>
@@ -5435,12 +6977,12 @@
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>732224CCL02</t>
+          <t>732224CC058</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>SARAN.R</t>
+          <t>YAZHINI SHREE A</t>
         </is>
       </c>
       <c r="D68" s="19" t="inlineStr">
@@ -5453,9 +6995,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>Saranraj_2580</t>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>yazhu_shree</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>PUBLIC_NOT_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H68" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="19" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -5465,12 +7029,12 @@
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>732224CCL03</t>
+          <t>732224CC059</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>SHREE SANJAY U K</t>
+          <t>YURJEEN J</t>
         </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
@@ -5483,9 +7047,31 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F69" s="19" t="inlineStr">
-        <is>
-          <t>shreesanjay</t>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>Yurjeen26</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="21" t="inlineStr">
+        <is>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -5495,12 +7081,12 @@
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>732224CCL04</t>
+          <t>732224CC060</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>SRIDHAR S</t>
+          <t>YUVANESH S</t>
         </is>
       </c>
       <c r="D70" s="19" t="inlineStr">
@@ -5513,19 +7099,41 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F70" s="19" t="inlineStr">
-        <is>
-          <t>sridhar320076</t>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>V0mg69rzpB</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ATTENDED</t>
+        </is>
+      </c>
+      <c r="H70" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="21" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5568,7 +7176,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -5582,7 +7190,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -5635,12 +7243,12 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>732224CC044</t>
+          <t>732224CC001</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>AJAY A</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -5653,12 +7261,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>sakthi0407</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>Ajay_a1277</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -5675,12 +7283,12 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>732224CC025</t>
+          <t>732224CC002</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>MAGUDAPATHI S</t>
+          <t>AMRUTHA M</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -5693,12 +7301,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>Magudapathi26</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Amruthauma</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -5715,12 +7323,12 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>732224CC021</t>
+          <t>732224CC003</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>KIRUTHIKAA P T</t>
+          <t>ANUSHKUMAR R</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -5733,19 +7341,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>KIRUTHIKAA_05</t>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>anushkumar_06</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -5755,12 +7363,12 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>732224CC047</t>
+          <t>732224CC004</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>SHARMILA P</t>
+          <t>BHARATH G</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -5773,19 +7381,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>Sharmila__27</t>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>BHARATH1927</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -5795,12 +7403,12 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>732224CC035</t>
+          <t>732224CC005</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>POOMITHA KS</t>
+          <t>DHANUSHYA G K</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -5813,19 +7421,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>Poomitha_23</t>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>dhanu2006</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -5835,12 +7443,12 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>732224CC017</t>
+          <t>732224CC006</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>JANANI S</t>
+          <t>DHARSHINI A M</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -5853,12 +7461,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>Jananii_26</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>DHARSHINI_1605</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -5875,12 +7483,12 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>732224CC048</t>
+          <t>732224CC007</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>SOWMIYA S</t>
+          <t>DHARSHINI S M</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -5893,19 +7501,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>Sowmiya_7383</t>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Dharshini90989</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -5915,12 +7523,12 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>732224CC029</t>
+          <t>732224CC008</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>MOHAMED THARIQ J</t>
+          <t>DHARUNRAJ K P</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -5933,12 +7541,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>Thariq2625</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>K_P_DHARUNRAJ</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -5955,12 +7563,12 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>732224CC002</t>
+          <t>732224CC009</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>AMRUTHA M</t>
+          <t>GIRIPATHI K</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -5973,12 +7581,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>Amruthauma</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>Giripathi_k</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -5995,12 +7603,12 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>732224CC027</t>
+          <t>732224CC010</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>MANJUNATH D</t>
+          <t>GOKUL P</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -6013,12 +7621,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>ByNXF6IdWN</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>gokul_5405</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -6035,12 +7643,12 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>732224CC001</t>
+          <t>732224CC011</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>AJAY A</t>
+          <t>HARDIKA M</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -6053,12 +7661,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>Ajay_a1277</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>hardi22011</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -6075,12 +7683,12 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>732224CC003</t>
+          <t>732224CC012</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>ANUSHKUMAR R</t>
+          <t>HARIHARAN S V</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -6093,12 +7701,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>anushkumar_06</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>x8ggzaR6Gx</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -6115,12 +7723,12 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>732224CC004</t>
+          <t>732224CC013</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>BHARATH G</t>
+          <t>HARISH K</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -6133,19 +7741,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>BHARATH1927</t>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>Harish000007</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6155,12 +7763,12 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>732224CC005</t>
+          <t>732224CC014</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>DHANUSHYA G K</t>
+          <t>HARISH KUMAAR S</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -6173,19 +7781,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>dhanu2006</t>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>HarishVichu</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6195,12 +7803,12 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>732224CC006</t>
+          <t>732224CC015</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>DHARSHINI A M</t>
+          <t>HARISH N</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -6213,19 +7821,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>DHARSHINI_1605</t>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>Har-ish23</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6235,12 +7843,12 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>732224CC007</t>
+          <t>732224CC016</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>DHARSHINI S M</t>
+          <t>INIYA K</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -6253,19 +7861,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>Dharshini90989</t>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>Iniya3126</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H23" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6275,12 +7883,12 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>732224CC008</t>
+          <t>732224CC017</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>DHARUNRAJ K P</t>
+          <t>JANANI S</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -6293,12 +7901,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>K_P_DHARUNRAJ</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>Jananii_26</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -6315,12 +7923,12 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>732224CC009</t>
+          <t>732224CC018</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>GIRIPATHI K</t>
+          <t>JAYAPRAKASH S</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -6333,19 +7941,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>Giripathi_k</t>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>jayaprakash2007</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6355,12 +7963,12 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>732224CC010</t>
+          <t>732224CC019</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>GOKUL P</t>
+          <t>JAYASURYA S</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -6373,19 +7981,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>gokul_5405</t>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>Surya1231172</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6395,12 +8003,12 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>732224CC011</t>
+          <t>732224CC020</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>HARDIKA M</t>
+          <t>KARTHIKEYAN V</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -6413,19 +8021,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>hardi22011</t>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>karthi_2007</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H27" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6435,12 +8043,12 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>732224CC012</t>
+          <t>732224CC021</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>HARIHARAN S V</t>
+          <t>KIRUTHIKAA P T</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
@@ -6453,19 +8061,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>x8ggzaR6Gx</t>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>KIRUTHIKAA_05</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6475,12 +8083,12 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>732224CC013</t>
+          <t>732224CC022</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>HARISH K</t>
+          <t>KISHORE C</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -6493,19 +8101,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>Harish000007</t>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>KISHORE_CHANDRAKUMAR</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6515,12 +8123,12 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>732224CC014</t>
+          <t>732224CC023</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>HARISH KUMAAR S</t>
+          <t>LAKSANA S</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
@@ -6533,19 +8141,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>HarishVichu</t>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>Laksana_Subramanian</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6555,12 +8163,12 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>732224CC015</t>
+          <t>732224CC024</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>HARISH N</t>
+          <t>MADAN PRASATH G</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
@@ -6573,12 +8181,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>Har-ish23</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -6595,12 +8203,12 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>732224CC016</t>
+          <t>732224CC025</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>INIYA K</t>
+          <t>MAGUDAPATHI S</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
@@ -6613,19 +8221,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>Iniya3126</t>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>Magudapathi26</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6635,12 +8243,12 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>732224CC018</t>
+          <t>732224CC026</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>JAYAPRAKASH S</t>
+          <t>MAHILNETHRA S K</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
@@ -6653,12 +8261,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>jayaprakash2007</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>mahilnethra</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -6675,12 +8283,12 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>732224CC019</t>
+          <t>732224CC027</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>JAYASURYA S</t>
+          <t>MANJUNATH D</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
@@ -6693,19 +8301,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>Surya1231172</t>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>ByNXF6IdWN</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6715,12 +8323,12 @@
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>732224CC020</t>
+          <t>732224CC028</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>KARTHIKEYAN V</t>
+          <t>MANOJ KUMAR C</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
@@ -6733,19 +8341,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>karthi_2007</t>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>ManojKumar2315</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H35" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6755,12 +8363,12 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>732224CC022</t>
+          <t>732224CC029</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>KISHORE C</t>
+          <t>MOHAMED THARIQ J</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
@@ -6773,12 +8381,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>KISHORE_CHANDRAKUMAR</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>Thariq2625</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -6795,12 +8403,12 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>732224CC023</t>
+          <t>732224CCL01</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>LAKSANA S</t>
+          <t>MOHAMMED AFFAN.JA</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -6813,12 +8421,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>Laksana_Subramanian</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>Mohammed_Affan_JA</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -6835,12 +8443,12 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>732224CC024</t>
+          <t>732224CC031</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>MADAN PRASATH G</t>
+          <t>NANTHISH S</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -6853,19 +8461,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>login</t>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>nanthishvaran_07</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6875,12 +8483,12 @@
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>732224CC026</t>
+          <t>732224CC032</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>MAHILNETHRA S K</t>
+          <t>NISHANTH J S</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
@@ -6893,12 +8501,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>mahilnethra</t>
-        </is>
-      </c>
-      <c r="G39" s="21" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>Nishanthjs</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -6915,12 +8523,12 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>732224CC028</t>
+          <t>732224CC033</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>MANOJ KUMAR C</t>
+          <t>NITHIN S</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -6933,12 +8541,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>ManojKumar2315</t>
-        </is>
-      </c>
-      <c r="G40" s="21" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>nithin_31_</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -6955,12 +8563,12 @@
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>732224CC031</t>
+          <t>732224CC034</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>NANTHISH S</t>
+          <t>NIVETHYTHA JR R</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -6973,19 +8581,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>nanthishvaran_07</t>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>Nivethytha0704</t>
         </is>
       </c>
       <c r="G41" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H41" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -6995,12 +8603,12 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>732224CC032</t>
+          <t>732224CC035</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>NISHANTH J S</t>
+          <t>POOMITHA KS</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -7013,19 +8621,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>Nishanthjs</t>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>Poomitha_23</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7035,12 +8643,12 @@
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>732224CC033</t>
+          <t>732224CC036</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>NITHIN S</t>
+          <t>PRASATH R</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -7053,12 +8661,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
-        <is>
-          <t>nithin_31_</t>
-        </is>
-      </c>
-      <c r="G43" s="21" t="inlineStr">
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>prasath00156</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7075,12 +8683,12 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>732224CC034</t>
+          <t>732224CC037</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>NIVETHYTHA JR R</t>
+          <t>PRITHIKA P</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -7093,12 +8701,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>Nivethytha0704</t>
-        </is>
-      </c>
-      <c r="G44" s="21" t="inlineStr">
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>Pritss2206</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7115,12 +8723,12 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>732224CC036</t>
+          <t>732224CC038</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>PRASATH R</t>
+          <t>RADHISRI N</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -7133,12 +8741,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F45" s="19" t="inlineStr">
-        <is>
-          <t>prasath00156</t>
-        </is>
-      </c>
-      <c r="G45" s="21" t="inlineStr">
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>Radhisri28</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7155,12 +8763,12 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>732224CC037</t>
+          <t>732224CC039</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>PRITHIKA P</t>
+          <t>RAJESH R</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
@@ -7173,19 +8781,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F46" s="19" t="inlineStr">
-        <is>
-          <t>Pritss2206</t>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>Rajesh1328</t>
         </is>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H46" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7195,12 +8803,12 @@
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>732224CC038</t>
+          <t>732224CC040</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>RADHISRI N</t>
+          <t>RITHANIKA V</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -7213,19 +8821,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F47" s="19" t="inlineStr">
-        <is>
-          <t>Radhisri28</t>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>Rithanika_Venakatachalam</t>
         </is>
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H47" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7235,12 +8843,12 @@
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>732224CC039</t>
+          <t>732224CC041</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>RAJESH R</t>
+          <t>RITHIKA J</t>
         </is>
       </c>
       <c r="D48" s="19" t="inlineStr">
@@ -7253,19 +8861,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F48" s="19" t="inlineStr">
-        <is>
-          <t>Rajesh1328</t>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>Rithu16122006</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H48" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7275,12 +8883,12 @@
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>732224CC040</t>
+          <t>732224CC042</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>RITHANIKA V</t>
+          <t>ROHITH R</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -7293,19 +8901,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F49" s="19" t="inlineStr">
-        <is>
-          <t>Rithanika_Venakatachalam</t>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>Rohith_2682006</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H49" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7315,12 +8923,12 @@
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>732224CC041</t>
+          <t>732224CC043</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>RITHIKA J</t>
+          <t>SABARI N</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
@@ -7333,12 +8941,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
-        <is>
-          <t>Rithu16122006</t>
-        </is>
-      </c>
-      <c r="G50" s="21" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>sabari43</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7355,12 +8963,12 @@
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>732224CC042</t>
+          <t>732224CC044</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>ROHITH R</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -7373,12 +8981,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
-        <is>
-          <t>Rohith_2682006</t>
-        </is>
-      </c>
-      <c r="G51" s="21" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>sakthi0407</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7395,12 +9003,12 @@
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>732224CC043</t>
+          <t>732224CCL02</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>SABARI N</t>
+          <t>SARAN.R</t>
         </is>
       </c>
       <c r="D52" s="19" t="inlineStr">
@@ -7413,19 +9021,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>sabari43</t>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>Saranraj_2580</t>
         </is>
       </c>
       <c r="G52" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H52" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7453,12 +9061,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F53" s="19" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
         <is>
           <t>shandeeshrp</t>
         </is>
       </c>
-      <c r="G53" s="21" t="inlineStr">
+      <c r="G53" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7493,12 +9101,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="F54" s="20" t="inlineStr">
         <is>
           <t>Priya_1410</t>
         </is>
       </c>
-      <c r="G54" s="21" t="inlineStr">
+      <c r="G54" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7515,12 +9123,12 @@
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>732224CC049</t>
+          <t>732224CC047</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>SRISELVAN P</t>
+          <t>SHARMILA P</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -7533,12 +9141,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
-        <is>
-          <t>SriselvanP</t>
-        </is>
-      </c>
-      <c r="G55" s="21" t="inlineStr">
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>Sharmila__27</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7555,12 +9163,12 @@
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>732224CC050</t>
+          <t>732224CCL03</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>SUBA SRI B</t>
+          <t>SHREE SANJAY U K</t>
         </is>
       </c>
       <c r="D56" s="19" t="inlineStr">
@@ -7573,19 +9181,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F56" s="19" t="inlineStr">
-        <is>
-          <t>suba_sri10</t>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>shreesanjay</t>
         </is>
       </c>
       <c r="G56" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7595,12 +9203,12 @@
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>732224CC051</t>
+          <t>732224CC048</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>SUBASH MURUGAN S</t>
+          <t>SOWMIYA S</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -7613,12 +9221,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
-        <is>
-          <t>subashmurugan212</t>
-        </is>
-      </c>
-      <c r="G57" s="21" t="inlineStr">
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>Sowmiya_7383</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7635,12 +9243,12 @@
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>732224CC052</t>
+          <t>732224CCL04</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>SUPRIYA K</t>
+          <t>SRIDHAR S</t>
         </is>
       </c>
       <c r="D58" s="19" t="inlineStr">
@@ -7653,19 +9261,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F58" s="19" t="inlineStr">
-        <is>
-          <t>SUPRIYA_2601</t>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>sridhar320076</t>
         </is>
       </c>
       <c r="G58" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7675,12 +9283,12 @@
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>732224CC053</t>
+          <t>732224CC049</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>SURESH S</t>
+          <t>SRISELVAN P</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -7693,12 +9301,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
-        <is>
-          <t>suresh11092006</t>
-        </is>
-      </c>
-      <c r="G59" s="21" t="inlineStr">
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>SriselvanP</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7715,12 +9323,12 @@
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>732224CC054</t>
+          <t>732224CC050</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>VARSHINI DEVI K</t>
+          <t>SUBA SRI B</t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
@@ -7733,12 +9341,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
-        <is>
-          <t>varshini_devi2006</t>
-        </is>
-      </c>
-      <c r="G60" s="21" t="inlineStr">
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>suba_sri10</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7755,12 +9363,12 @@
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>732224CC055</t>
+          <t>732224CC051</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>VEDHASREE P</t>
+          <t>SUBASH MURUGAN S</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -7773,19 +9381,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>vedhasree_2006</t>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>subashmurugan212</t>
         </is>
       </c>
       <c r="G61" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H61" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7795,12 +9403,12 @@
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>732224CC056</t>
+          <t>732224CC052</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>VIGNESH T</t>
+          <t>SUPRIYA K</t>
         </is>
       </c>
       <c r="D62" s="19" t="inlineStr">
@@ -7813,12 +9421,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
-        <is>
-          <t>vignesh_1112</t>
-        </is>
-      </c>
-      <c r="G62" s="21" t="inlineStr">
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>SUPRIYA_2601</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7835,12 +9443,12 @@
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>732224CC057</t>
+          <t>732224CC053</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>VISHAANTH M B</t>
+          <t>SURESH S</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -7853,19 +9461,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
-        <is>
-          <t>vishaanth0007</t>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>suresh11092006</t>
         </is>
       </c>
       <c r="G63" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H63" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7875,12 +9483,12 @@
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>732224CC058</t>
+          <t>732224CC054</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>YAZHINI SHREE A</t>
+          <t>VARSHINI DEVI K</t>
         </is>
       </c>
       <c r="D64" s="19" t="inlineStr">
@@ -7893,12 +9501,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
-        <is>
-          <t>yazhu_shree</t>
-        </is>
-      </c>
-      <c r="G64" s="21" t="inlineStr">
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>varshini_devi2006</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr">
         <is>
           <t>PUBLIC_NOT_ATTENDED</t>
         </is>
@@ -7915,12 +9523,12 @@
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>732224CC059</t>
+          <t>732224CC055</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>YURJEEN J</t>
+          <t>VEDHASREE P</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -7933,12 +9541,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F65" s="19" t="inlineStr">
-        <is>
-          <t>Yurjeen26</t>
-        </is>
-      </c>
-      <c r="G65" s="22" t="inlineStr">
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>vedhasree_2006</t>
+        </is>
+      </c>
+      <c r="G65" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -7955,12 +9563,12 @@
       </c>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>732224CC060</t>
+          <t>732224CC056</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>YUVANESH S</t>
+          <t>VIGNESH T</t>
         </is>
       </c>
       <c r="D66" s="19" t="inlineStr">
@@ -7973,19 +9581,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
-        <is>
-          <t>V0mg69rzpB</t>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>vignesh_1112</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H66" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -7995,12 +9603,12 @@
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>732224CCL01</t>
+          <t>732224CC057</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>MOHAMMED AFFAN.JA</t>
+          <t>VISHAANTH M B</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -8013,19 +9621,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>Mohammed_Affan_JA</t>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>vishaanth0007</t>
         </is>
       </c>
       <c r="G67" s="21" t="inlineStr">
         <is>
-          <t>PUBLIC_NOT_ATTENDED</t>
+          <t>OFFICIAL_ATTENDED</t>
         </is>
       </c>
       <c r="H67" s="19" t="inlineStr">
         <is>
-          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
+          <t>VERIFIED_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -8035,12 +9643,12 @@
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>732224CCL02</t>
+          <t>732224CC058</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>SARAN.R</t>
+          <t>YAZHINI SHREE A</t>
         </is>
       </c>
       <c r="D68" s="19" t="inlineStr">
@@ -8053,19 +9661,19 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>Saranraj_2580</t>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>yazhu_shree</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr">
         <is>
-          <t>OFFICIAL_ATTENDED</t>
+          <t>PUBLIC_NOT_ATTENDED</t>
         </is>
       </c>
       <c r="H68" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED_CONTEST_EVIDENCE</t>
+          <t>NO_PUBLIC_CONTEST_EVIDENCE</t>
         </is>
       </c>
     </row>
@@ -8075,12 +9683,12 @@
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>732224CCL03</t>
+          <t>732224CC059</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>SHREE SANJAY U K</t>
+          <t>YURJEEN J</t>
         </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
@@ -8093,12 +9701,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F69" s="19" t="inlineStr">
-        <is>
-          <t>shreesanjay</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="inlineStr">
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>Yurjeen26</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8115,12 +9723,12 @@
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>732224CCL04</t>
+          <t>732224CC060</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>SRIDHAR S</t>
+          <t>YUVANESH S</t>
         </is>
       </c>
       <c r="D70" s="19" t="inlineStr">
@@ -8133,12 +9741,12 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F70" s="19" t="inlineStr">
-        <is>
-          <t>sridhar320076</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr">
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>V0mg69rzpB</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8202,7 +9810,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -8216,7 +9824,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -8357,7 +9965,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8374,12 +9982,12 @@
       <c r="J9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L9" s="22" t="n">
+      <c r="L9" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8407,7 +10015,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8424,12 +10032,12 @@
       <c r="J10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L10" s="22" t="n">
+      <c r="L10" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8507,7 +10115,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8524,12 +10132,12 @@
       <c r="J12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L12" s="22" t="n">
+      <c r="L12" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8557,7 +10165,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8574,12 +10182,12 @@
       <c r="J13" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L13" s="22" t="n">
+      <c r="L13" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -8657,7 +10265,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8674,12 +10282,12 @@
       <c r="J15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L15" s="22" t="n">
+      <c r="L15" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8707,7 +10315,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8724,12 +10332,12 @@
       <c r="J16" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L16" s="22" t="n">
+      <c r="L16" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -8757,7 +10365,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8774,12 +10382,12 @@
       <c r="J17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L17" s="22" t="n">
+      <c r="L17" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8907,7 +10515,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -8924,12 +10532,12 @@
       <c r="J20" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="22" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L20" s="22" t="n">
+      <c r="L20" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9007,7 +10615,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9024,12 +10632,12 @@
       <c r="J22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="22" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L22" s="22" t="n">
+      <c r="L22" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -9057,7 +10665,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9074,12 +10682,12 @@
       <c r="J23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
-      <c r="L23" s="22" t="n">
+      <c r="L23" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9107,7 +10715,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9124,12 +10732,12 @@
       <c r="J24" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="22" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L24" s="22" t="n">
+      <c r="L24" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9157,7 +10765,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9174,12 +10782,12 @@
       <c r="J25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L25" s="22" t="n">
+      <c r="L25" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -9207,7 +10815,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9224,12 +10832,12 @@
       <c r="J26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="22" t="inlineStr">
+      <c r="K26" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L26" s="22" t="n">
+      <c r="L26" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9407,7 +11015,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9424,12 +11032,12 @@
       <c r="J30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="22" t="inlineStr">
+      <c r="K30" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L30" s="22" t="n">
+      <c r="L30" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9657,7 +11265,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9674,12 +11282,12 @@
       <c r="J35" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="22" t="inlineStr">
+      <c r="K35" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L35" s="22" t="n">
+      <c r="L35" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -9707,7 +11315,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9724,12 +11332,12 @@
       <c r="J36" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="22" t="inlineStr">
+      <c r="K36" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L36" s="22" t="n">
+      <c r="L36" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -9957,7 +11565,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -9974,12 +11582,12 @@
       <c r="J41" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="22" t="inlineStr">
+      <c r="K41" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L41" s="22" t="n">
+      <c r="L41" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -10307,7 +11915,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F48" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -10324,12 +11932,12 @@
       <c r="J48" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K48" s="22" t="inlineStr">
+      <c r="K48" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L48" s="22" t="n">
+      <c r="L48" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10357,7 +11965,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F49" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -10374,12 +11982,12 @@
       <c r="J49" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="22" t="inlineStr">
+      <c r="K49" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L49" s="22" t="n">
+      <c r="L49" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -10957,7 +12565,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F61" s="22" t="inlineStr">
+      <c r="F61" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -10974,12 +12582,12 @@
       <c r="J61" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="22" t="inlineStr">
+      <c r="K61" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L61" s="22" t="n">
+      <c r="L61" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -11057,7 +12665,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F63" s="22" t="inlineStr">
+      <c r="F63" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -11074,12 +12682,12 @@
       <c r="J63" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K63" s="22" t="inlineStr">
+      <c r="K63" s="21" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
-      <c r="L63" s="22" t="n">
+      <c r="L63" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11157,7 +12765,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F65" s="22" t="inlineStr">
+      <c r="F65" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -11174,12 +12782,12 @@
       <c r="J65" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K65" s="22" t="inlineStr">
+      <c r="K65" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L65" s="22" t="n">
+      <c r="L65" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -11207,7 +12815,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F66" s="22" t="inlineStr">
+      <c r="F66" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -11224,12 +12832,12 @@
       <c r="J66" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K66" s="22" t="inlineStr">
+      <c r="K66" s="21" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="L66" s="22" t="n">
+      <c r="L66" s="21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -11307,7 +12915,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F68" s="22" t="inlineStr">
+      <c r="F68" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -11324,12 +12932,12 @@
       <c r="J68" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K68" s="22" t="inlineStr">
+      <c r="K68" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L68" s="22" t="n">
+      <c r="L68" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -11357,7 +12965,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F69" s="22" t="inlineStr">
+      <c r="F69" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -11374,12 +12982,12 @@
       <c r="J69" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="22" t="inlineStr">
+      <c r="K69" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L69" s="22" t="n">
+      <c r="L69" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -11407,7 +13015,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F70" s="22" t="inlineStr">
+      <c r="F70" s="21" t="inlineStr">
         <is>
           <t>OFFICIAL_ATTENDED</t>
         </is>
@@ -11424,12 +13032,12 @@
       <c r="J70" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K70" s="22" t="inlineStr">
+      <c r="K70" s="21" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
-      <c r="L70" s="22" t="n">
+      <c r="L70" s="21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -11486,21 +13094,21 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>WEEKLY CONTEST 516 — INSTITUTIONAL TOP PERFORMERS LEADERBOARD</t>
+          <t>WEEKLY CONTEST 516 — TOP PERFORMERS LEADERBOARD (4/4 -&gt; 3/4 -&gt; 2/4 -&gt; 1/4)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -11591,7 +13199,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Amruthauma</t>
         </is>
@@ -11641,7 +13249,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>BHARATH1927</t>
         </is>
@@ -11691,7 +13299,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>K_P_DHARUNRAJ</t>
         </is>
@@ -11741,7 +13349,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>gokul_5405</t>
         </is>
@@ -11791,7 +13399,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>HarishVichu</t>
         </is>
@@ -11841,7 +13449,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Jananii_26</t>
         </is>
@@ -11891,7 +13499,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>Rajesh1328</t>
         </is>
@@ -11941,7 +13549,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>Saranraj_2580</t>
         </is>
@@ -11991,7 +13599,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>shreesanjay</t>
         </is>
@@ -12041,7 +13649,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>sridhar320076</t>
         </is>
@@ -12091,7 +13699,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Yurjeen26</t>
         </is>
@@ -12141,7 +13749,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>DHARSHINI_1605</t>
         </is>
@@ -12191,7 +13799,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>Giripathi_k</t>
         </is>
@@ -12241,7 +13849,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>karthi_2007</t>
         </is>
@@ -12291,7 +13899,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>KIRUTHIKAA_05</t>
         </is>
@@ -12341,7 +13949,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>KISHORE_CHANDRAKUMAR</t>
         </is>
@@ -12391,7 +13999,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>Magudapathi26</t>
         </is>
@@ -12441,7 +14049,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>ByNXF6IdWN</t>
         </is>
@@ -12491,7 +14099,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>Thariq2625</t>
         </is>
@@ -12541,7 +14149,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>nanthishvaran_07</t>
         </is>
@@ -12591,7 +14199,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>Poomitha_23</t>
         </is>
@@ -12641,7 +14249,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>Rithanika_Venakatachalam</t>
         </is>
@@ -12691,7 +14299,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>vedhasree_2006</t>
         </is>
@@ -12741,7 +14349,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>V0mg69rzpB</t>
         </is>
@@ -12791,7 +14399,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>Dharshini90989</t>
         </is>
@@ -12841,7 +14449,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>vishaanth0007</t>
         </is>
@@ -12869,11 +14477,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -12920,7 +14528,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -12934,7 +14542,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -13003,11 +14611,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -13054,7 +14662,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -13068,7 +14676,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -13159,7 +14767,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Amruthauma</t>
         </is>
@@ -13209,7 +14817,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>BHARATH1927</t>
         </is>
@@ -13259,7 +14867,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>K_P_DHARUNRAJ</t>
         </is>
@@ -13309,7 +14917,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>gokul_5405</t>
         </is>
@@ -13359,7 +14967,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>HarishVichu</t>
         </is>
@@ -13409,7 +15017,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Jananii_26</t>
         </is>
@@ -13459,7 +15067,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>Rajesh1328</t>
         </is>
@@ -13509,7 +15117,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>Saranraj_2580</t>
         </is>
@@ -13559,7 +15167,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>shreesanjay</t>
         </is>
@@ -13609,7 +15217,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>sridhar320076</t>
         </is>
@@ -13659,7 +15267,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Yurjeen26</t>
         </is>
@@ -13687,11 +15295,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -13738,7 +15346,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -13752,7 +15360,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -13843,7 +15451,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>DHARSHINI_1605</t>
         </is>
@@ -13893,7 +15501,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>Giripathi_k</t>
         </is>
@@ -13943,7 +15551,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>karthi_2007</t>
         </is>
@@ -13993,7 +15601,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>KIRUTHIKAA_05</t>
         </is>
@@ -14043,7 +15651,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>KISHORE_CHANDRAKUMAR</t>
         </is>
@@ -14093,7 +15701,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Magudapathi26</t>
         </is>
@@ -14143,7 +15751,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>ByNXF6IdWN</t>
         </is>
@@ -14193,7 +15801,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>Thariq2625</t>
         </is>
@@ -14243,7 +15851,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>nanthishvaran_07</t>
         </is>
@@ -14293,7 +15901,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>Poomitha_23</t>
         </is>
@@ -14343,7 +15951,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Rithanika_Venakatachalam</t>
         </is>
@@ -14393,7 +16001,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>vedhasree_2006</t>
         </is>
@@ -14443,7 +16051,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>V0mg69rzpB</t>
         </is>
@@ -14471,11 +16079,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14522,7 +16130,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ALL 11 INSTITUTIONAL DEPARTMENTS &amp; COHORTS</t>
+          <t>DEPARTMENT OF CSE(CS) • III YEAR</t>
         </is>
       </c>
     </row>
@@ -14536,7 +16144,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Institutional Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:17 AM IST</t>
+          <t>Contest Name: Weekly Contest 516   |   Session Date: 23.08.2026   |   Academic Year: 2026–2027   |   Roster Scope: 63 Students   |   Official Window: 08:00 AM – 09:30 AM IST   |   Generated At: 23 Aug 2026, 10:21 AM IST</t>
         </is>
       </c>
     </row>
@@ -14627,7 +16235,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Dharshini90989</t>
         </is>
@@ -14677,7 +16285,7 @@
           <t>III</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>vishaanth0007</t>
         </is>
@@ -14705,11 +16313,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
